--- a/data/trans_orig/P15E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,62 +2246,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4741</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43189</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62366</t>
+          <t>62743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78462</t>
+          <t>78283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>772</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50613</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>77555</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
